--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.25</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.6258992805755396</v>
       </c>
       <c r="D2">
-        <v>0.625</v>
+        <v>0.4031007751937984</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6470588235294118</v>
+        <v>0.75</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6258992805755396</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="D2">
-        <v>0.4031007751937984</v>
+        <v>0.3305785123966942</v>
       </c>
       <c r="E2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
